--- a/artfynd/A 50647-2025 artfynd.xlsx
+++ b/artfynd/A 50647-2025 artfynd.xlsx
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106112029</v>
+        <v>106111950</v>
       </c>
       <c r="B2" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>586551.3643703077</v>
+        <v>586526</v>
       </c>
       <c r="R2" t="n">
-        <v>6388322.624097819</v>
+        <v>6388315</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,24 +755,14 @@
           <t>2023-01-22</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-01-22</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Kvarnsjön.</t>
+          <t>Kvarnsjön</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,15 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106111950</v>
+        <v>106111985</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -840,7 +820,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -857,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586525.7660592019</v>
+        <v>586552</v>
       </c>
       <c r="R3" t="n">
-        <v>6388315.114269454</v>
+        <v>6388342</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,19 +870,9 @@
           <t>2023-01-22</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-01-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -935,42 +905,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>106111985</v>
+        <v>106112029</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -987,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586552.0138581712</v>
+        <v>586551</v>
       </c>
       <c r="R4" t="n">
-        <v>6388342.455347065</v>
+        <v>6388323</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,24 +985,14 @@
           <t>2023-01-22</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-01-22</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Kvarnsjön</t>
+          <t>Kvarnsjön.</t>
         </is>
       </c>
       <c r="AD4" t="b">
